--- a/target/classes/rahulshettyacadamy/Data/Data.xlsx
+++ b/target/classes/rahulshettyacadamy/Data/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Testing\Sele\SeleniumFrameWorkDesign2\src\main\java\rahulshettyacadamy\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44B423E-465D-4C43-83C8-1BE7880524D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F09E37A-2BB3-4FD1-B5D3-18D25DD3D9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Email</t>
   </si>
@@ -99,13 +99,10 @@
     <t>raju1245653@gmail.com</t>
   </si>
   <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>Female</t>
   </si>
   <si>
-    <t>sdfghjk</t>
+    <t>raju1245@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -535,7 +532,7 @@
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -578,7 +575,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -602,7 +599,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>22</v>
